--- a/随笔/学习规划.xlsx
+++ b/随笔/学习规划.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\kaoyan\随笔\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80BB572C-3832-49B1-92C6-4154FE94D64E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7A0C0E6-3DC5-4BFE-9D86-5D6E37CE9AFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{4319DEF0-80FA-42CA-B3F2-4B39103C2D0C}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
   <si>
     <t>计划下一次复习</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -68,6 +68,14 @@
   </si>
   <si>
     <t>暂无计划</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>求幂级数的收敛域</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>求幂级数的和函数</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -114,11 +122,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -435,7 +446,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E225AF1A-6DD8-49A1-9FF6-8F01D24A7B26}">
-  <dimension ref="A2:E6"/>
+  <dimension ref="A2:E8"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.5" customWidth="1"/>
@@ -463,7 +474,7 @@
       <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C3" s="1">
@@ -478,7 +489,7 @@
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C4" s="1">
@@ -492,7 +503,7 @@
       <c r="A5" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="1">
@@ -503,11 +514,27 @@
       <c r="A6" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C6" t="s">
         <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="2">
+        <v>46310</v>
+      </c>
+      <c r="C7" s="1">
+        <v>46313</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/随笔/学习规划.xlsx
+++ b/随笔/学习规划.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\kaoyan\随笔\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7A0C0E6-3DC5-4BFE-9D86-5D6E37CE9AFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16681605-1A2A-4558-90D8-FF7E5F517041}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{4319DEF0-80FA-42CA-B3F2-4B39103C2D0C}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
   <si>
     <t>计划下一次复习</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -47,10 +47,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>傅里叶级数提取练习</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 2026/10/13</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -67,15 +63,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>暂无计划</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>求幂级数的收敛域</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>求幂级数的和函数</t>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>傅里叶级数提取练习和傅里叶级数的题目</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重要：求幂级数的和函数+把函数展开为 x-x_0 的幂级数（880P50:(5)到(10)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -122,14 +122,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -446,12 +443,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E225AF1A-6DD8-49A1-9FF6-8F01D24A7B26}">
-  <dimension ref="A2:E8"/>
+  <dimension ref="A2:E9"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="23.5" customWidth="1"/>
+    <col min="1" max="1" width="60.25" customWidth="1"/>
     <col min="2" max="2" width="12.875" customWidth="1"/>
-    <col min="3" max="3" width="15.25" customWidth="1"/>
+    <col min="3" max="3" width="19" customWidth="1"/>
     <col min="4" max="4" width="17.875" customWidth="1"/>
     <col min="5" max="5" width="12.875" customWidth="1"/>
   </cols>
@@ -461,20 +458,20 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C3" s="1">
@@ -489,8 +486,8 @@
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>4</v>
+      <c r="B4" s="1">
+        <v>46309</v>
       </c>
       <c r="C4" s="1">
         <v>46312</v>
@@ -501,10 +498,10 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="2" t="s">
         <v>6</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>5</v>
       </c>
       <c r="C5" s="1">
         <v>46312</v>
@@ -512,29 +509,40 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C6" t="s">
-        <v>10</v>
+      <c r="C6" s="1">
+        <v>46314</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="2">
+        <v>9</v>
+      </c>
+      <c r="B7" s="1">
         <v>46310</v>
       </c>
       <c r="C7" s="1">
         <v>46313</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>12</v>
+      </c>
+      <c r="B8" s="1">
+        <v>46311</v>
+      </c>
+      <c r="C8" s="1">
+        <v>46314</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/随笔/学习规划.xlsx
+++ b/随笔/学习规划.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\kaoyan\随笔\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16681605-1A2A-4558-90D8-FF7E5F517041}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A1C45AB-69D5-4190-9F72-4532D1347BBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{4319DEF0-80FA-42CA-B3F2-4B39103C2D0C}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
   <si>
     <t>计划下一次复习</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -47,10 +47,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 2026/10/13</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>无穷级数提取练习</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -63,19 +59,31 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>求幂级数的收敛域</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>傅里叶级数提取练习和傅里叶级数的题目</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>重要：求幂级数的和函数+把函数展开为 x-x_0 的幂级数（880P50:(5)到(10)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026/10/xx</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2026/10/17</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>求幂级数的收敛域 8道题</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">微分方程提取练习 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 微分方程的某些题目</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -443,11 +451,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E225AF1A-6DD8-49A1-9FF6-8F01D24A7B26}">
-  <dimension ref="A2:E9"/>
+  <dimension ref="A2:E10"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="60.25" customWidth="1"/>
-    <col min="2" max="2" width="12.875" customWidth="1"/>
+    <col min="2" max="2" width="13" customWidth="1"/>
     <col min="3" max="3" width="19" customWidth="1"/>
     <col min="4" max="4" width="17.875" customWidth="1"/>
     <col min="5" max="5" width="12.875" customWidth="1"/>
@@ -458,13 +466,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
@@ -487,29 +495,29 @@
         <v>3</v>
       </c>
       <c r="B4" s="1">
-        <v>46309</v>
+        <v>46312</v>
       </c>
       <c r="C4" s="1">
-        <v>46312</v>
-      </c>
-      <c r="D4" s="1">
         <v>46317</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C5" s="1">
-        <v>46312</v>
+        <v>46317</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>4</v>
@@ -520,7 +528,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B7" s="1">
         <v>46310</v>
@@ -531,7 +539,7 @@
     </row>
     <row r="8" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B8" s="1">
         <v>46311</v>
@@ -542,7 +550,24 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>13</v>
+      </c>
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="1">
+        <v>46312</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="1">
+        <v>46312</v>
+      </c>
+      <c r="C10" s="1">
+        <v>46313</v>
       </c>
     </row>
   </sheetData>

--- a/随笔/学习规划.xlsx
+++ b/随笔/学习规划.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\kaoyan\随笔\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A1C45AB-69D5-4190-9F72-4532D1347BBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85D0EF23-421C-487C-8882-33916B62801A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{4319DEF0-80FA-42CA-B3F2-4B39103C2D0C}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
   <si>
     <t>计划下一次复习</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -84,6 +84,30 @@
   </si>
   <si>
     <t xml:space="preserve"> 微分方程的某些题目</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2026/10/18</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>22-26历年关于无穷级数的真题</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>学习次数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中央处理器提取练习</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指令系统提取练习</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IO 系统</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -451,122 +475,188 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E225AF1A-6DD8-49A1-9FF6-8F01D24A7B26}">
-  <dimension ref="A2:E10"/>
+  <dimension ref="A2:F16"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="60.25" customWidth="1"/>
-    <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="3" max="3" width="19" customWidth="1"/>
-    <col min="4" max="4" width="17.875" customWidth="1"/>
-    <col min="5" max="5" width="12.875" customWidth="1"/>
+    <col min="1" max="1" width="50.25" customWidth="1"/>
+    <col min="2" max="2" width="9.625" customWidth="1"/>
+    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="4" max="4" width="19" customWidth="1"/>
+    <col min="5" max="5" width="17.875" customWidth="1"/>
+    <col min="6" max="6" width="12.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>0</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="1">
-        <v>46313</v>
-      </c>
       <c r="D3" s="1">
+        <v>46314</v>
+      </c>
+      <c r="E3" s="1">
         <v>46319</v>
       </c>
-      <c r="E3" s="1"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F3" s="1"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4" s="1">
         <v>46312</v>
       </c>
-      <c r="C4" s="1">
+      <c r="D4" s="1">
         <v>46317</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="1">
+      <c r="D5" s="1">
         <v>46317</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="1">
-        <v>46314</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="1">
-        <v>46310</v>
+      <c r="B7">
+        <v>1</v>
       </c>
       <c r="C7" s="1">
         <v>46313</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D7" s="1">
+        <v>46313</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8" s="1">
         <v>46311</v>
       </c>
-      <c r="C8" s="1">
+      <c r="D8" s="1">
         <v>46314</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>13</v>
       </c>
-      <c r="B9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="1">
-        <v>46312</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="1">
+        <v>46318</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10" s="1">
         <v>46312</v>
       </c>
-      <c r="C10" s="1">
+      <c r="D10" s="1">
+        <v>46313</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="1">
+        <v>46316</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13" s="1">
+        <v>46313</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="1">
         <v>46313</v>
       </c>
     </row>

--- a/随笔/学习规划.xlsx
+++ b/随笔/学习规划.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\kaoyan\随笔\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85D0EF23-421C-487C-8882-33916B62801A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DD7FEB1-49C1-4B1D-A652-23ACB407ADA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{4319DEF0-80FA-42CA-B3F2-4B39103C2D0C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{4319DEF0-80FA-42CA-B3F2-4B39103C2D0C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
   <si>
     <t>计划下一次复习</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -108,6 +108,18 @@
   </si>
   <si>
     <t>IO 系统</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无穷级数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>微分方程</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IO 方式</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -132,12 +144,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -154,11 +172,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -475,10 +496,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E225AF1A-6DD8-49A1-9FF6-8F01D24A7B26}">
-  <dimension ref="A2:F16"/>
+  <dimension ref="A2:F20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="50.25" customWidth="1"/>
+    <col min="1" max="1" width="61.875" customWidth="1"/>
     <col min="2" max="2" width="9.625" customWidth="1"/>
     <col min="3" max="3" width="13" customWidth="1"/>
     <col min="4" max="4" width="19" customWidth="1"/>
@@ -504,160 +525,184 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="1">
-        <v>46314</v>
-      </c>
-      <c r="E3" s="1">
-        <v>46319</v>
-      </c>
-      <c r="F3" s="1"/>
+      <c r="A3" s="2" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4">
         <v>2</v>
       </c>
-      <c r="C4" s="1">
-        <v>46312</v>
+      <c r="C4" s="1" t="s">
+        <v>4</v>
       </c>
       <c r="D4" s="1">
-        <v>46317</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>10</v>
-      </c>
+        <v>46314</v>
+      </c>
+      <c r="E4" s="1">
+        <v>46319</v>
+      </c>
+      <c r="F4" s="1"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>11</v>
+        <v>2</v>
+      </c>
+      <c r="C5" s="1">
+        <v>46312</v>
       </c>
       <c r="D5" s="1">
         <v>46317</v>
       </c>
+      <c r="E5" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="D6" s="1">
+        <v>46317</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
         <v>12</v>
       </c>
-      <c r="B7">
+      <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="C8" s="1">
+        <v>46315</v>
+      </c>
+      <c r="D8" s="1">
+        <v>46333</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
         <v>1</v>
       </c>
-      <c r="C7" s="1">
-        <v>46313</v>
-      </c>
-      <c r="D7" s="1">
-        <v>46313</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8" s="1">
+      <c r="C9" s="1">
         <v>46311</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D9" s="1">
         <v>46314</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
+    <row r="10" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+    </row>
+    <row r="11" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
         <v>13</v>
       </c>
-      <c r="B9">
+      <c r="B12">
         <v>2</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C12" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D12" s="1">
         <v>46318</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="C10" s="1">
-        <v>46312</v>
-      </c>
-      <c r="D10" s="1">
-        <v>46313</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" s="1">
-        <v>46316</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B13">
         <v>1</v>
       </c>
       <c r="C13" s="1">
+        <v>46312</v>
+      </c>
+      <c r="D13" s="1">
         <v>46313</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>16</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" s="1">
+        <v>46316</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16">
+        <v>2</v>
+      </c>
+      <c r="C16" s="1">
+        <v>46314</v>
+      </c>
+      <c r="D16" s="1">
+        <v>46319</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="1">
+      <c r="C19" s="1">
         <v>46313</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
